--- a/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:55:19+00:00</t>
+    <t>2026-10-29T04:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-imaging-attention-conditions-response</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-imaging-attention-conditions-response</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -565,7 +565,7 @@
     <t>Needed to allow editing of the questionnaire response in a manner that enforces the constraints of the original form.</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/Questionnaire/be-questionnaire-imaging-attention-conditions</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/Questionnaire/be-questionnaire-imaging-attention-conditions</t>
   </si>
   <si>
     <t>Event.instantiates</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:33:29+00:00</t>
+    <t>2026-10-29T04:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:45:11+00:00</t>
+    <t>2026-10-29T06:41:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:41:01+00:00</t>
+    <t>2026-10-29T06:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:43:17+00:00</t>
+    <t>2026-10-29T07:36:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-imaging-attention-conditions-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:36:53+00:00</t>
+    <t>2026-10-29T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
